--- a/data/loads.xlsx
+++ b/data/loads.xlsx
@@ -1,34 +1,115 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
-  <workbookProtection/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Keks-repo\KEKS\data\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56D3FF1F-8156-4B54-8110-95957B8D63D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView xWindow="3015" yWindow="1590" windowWidth="21600" windowHeight="13185" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0"/>
 </workbook>
 </file>
 
+<file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+  <si>
+    <t>name</t>
+  </si>
+  <si>
+    <t>bus</t>
+  </si>
+  <si>
+    <t>carrier</t>
+  </si>
+  <si>
+    <t>p_max</t>
+  </si>
+  <si>
+    <t>industry</t>
+  </si>
+  <si>
+    <t>Industry_1</t>
+  </si>
+  <si>
+    <t>kritis</t>
+  </si>
+  <si>
+    <t>Kritis_1</t>
+  </si>
+  <si>
+    <t>residential</t>
+  </si>
+  <si>
+    <t>Residential_1</t>
+  </si>
+  <si>
+    <t>industry_thermal</t>
+  </si>
+  <si>
+    <t>Industry_1_thermal</t>
+  </si>
+  <si>
+    <t>kritis_thermal</t>
+  </si>
+  <si>
+    <t>Kritis_1_thermal</t>
+  </si>
+  <si>
+    <t>residential_thermal</t>
+  </si>
+  <si>
+    <t>Residential_1_thermal</t>
+  </si>
+  <si>
+    <t>residential2_thermal</t>
+  </si>
+  <si>
+    <t>residential2</t>
+  </si>
+  <si>
+    <t>Residential_2</t>
+  </si>
+  <si>
+    <t>Residential_2_thermal</t>
+  </si>
+  <si>
+    <t>residential_3</t>
+  </si>
+  <si>
+    <t>residential3_thermal</t>
+  </si>
+  <si>
+    <t>Residential_3</t>
+  </si>
+  <si>
+    <t>Residential_3_thermal</t>
+  </si>
+</sst>
+</file>
+
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="0"/>
-  <fonts count="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="1" x14ac:knownFonts="1">
     <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <color theme="1"/>
-      <sz val="11"/>
       <scheme val="minor"/>
     </font>
   </fonts>
   <fills count="2">
     <fill>
-      <patternFill/>
+      <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
@@ -47,80 +128,21 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="1">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
+  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
-  <colors>
-    <indexedColors>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00000000"/>
-      <rgbColor rgb="00FFFFFF"/>
-      <rgbColor rgb="00FF0000"/>
-      <rgbColor rgb="0000FF00"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008000"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00808000"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="00C0C0C0"/>
-      <rgbColor rgb="00808080"/>
-      <rgbColor rgb="009999FF"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00FFFFCC"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00660066"/>
-      <rgbColor rgb="00FF8080"/>
-      <rgbColor rgb="000066CC"/>
-      <rgbColor rgb="00CCCCFF"/>
-      <rgbColor rgb="00000080"/>
-      <rgbColor rgb="00FF00FF"/>
-      <rgbColor rgb="00FFFF00"/>
-      <rgbColor rgb="0000FFFF"/>
-      <rgbColor rgb="00800080"/>
-      <rgbColor rgb="00800000"/>
-      <rgbColor rgb="00008080"/>
-      <rgbColor rgb="000000FF"/>
-      <rgbColor rgb="0000CCFF"/>
-      <rgbColor rgb="00CCFFFF"/>
-      <rgbColor rgb="00CCFFCC"/>
-      <rgbColor rgb="00FFFF99"/>
-      <rgbColor rgb="0099CCFF"/>
-      <rgbColor rgb="00FF99CC"/>
-      <rgbColor rgb="00CC99FF"/>
-      <rgbColor rgb="00FFCC99"/>
-      <rgbColor rgb="003366FF"/>
-      <rgbColor rgb="0033CCCC"/>
-      <rgbColor rgb="0099CC00"/>
-      <rgbColor rgb="00FFCC00"/>
-      <rgbColor rgb="00FF9900"/>
-      <rgbColor rgb="00FF6600"/>
-      <rgbColor rgb="00666699"/>
-      <rgbColor rgb="00969696"/>
-      <rgbColor rgb="00003366"/>
-      <rgbColor rgb="00339966"/>
-      <rgbColor rgb="00003300"/>
-      <rgbColor rgb="00333300"/>
-      <rgbColor rgb="00993300"/>
-      <rgbColor rgb="00993366"/>
-      <rgbColor rgb="00333399"/>
-      <rgbColor rgb="00333333"/>
-    </indexedColors>
-  </colors>
+  <extLst>
+    <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
+      <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
+    </ext>
+    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
+      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
+    </ext>
+  </extLst>
 </styleSheet>
 </file>
 
@@ -408,130 +430,120 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr/>
-  </sheetPr>
-  <dimension ref="A1:D7"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1">
-      <c r="A1" t="inlineStr">
-        <is>
-          <t>name</t>
-        </is>
-      </c>
-      <c r="B1" t="inlineStr">
-        <is>
-          <t>bus</t>
-        </is>
-      </c>
-      <c r="C1" t="inlineStr">
-        <is>
-          <t>carrier</t>
-        </is>
-      </c>
-      <c r="D1" t="inlineStr">
-        <is>
-          <t>p_max</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>industry</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>Industry_1</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr"/>
-      <c r="D2" t="n">
-        <v>0.05696</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>kritis</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>Kritis_1</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr"/>
-      <c r="D3" t="n">
-        <v>0.006059999999999999</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>residential</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>Residential_1</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr"/>
-      <c r="D4" t="n">
-        <v>0.06669</v>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>industry_thermal</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>Industry_1_thermal</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr"/>
-      <c r="D5" t="n">
-        <v>0.17511</v>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>kritis_thermal</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>Kritis_1_thermal</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="n">
-        <v>0.04188</v>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>residential_thermal</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>Residential_1_thermal</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="n">
-        <v>2.11129</v>
+    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A2" t="s">
+        <v>4</v>
+      </c>
+      <c r="B2" t="s">
+        <v>5</v>
+      </c>
+      <c r="D2">
+        <v>5.6959999999999997E-2</v>
+      </c>
+    </row>
+    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
+        <v>7</v>
+      </c>
+      <c r="D3">
+        <v>6.0599999999999994E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
+        <v>9</v>
+      </c>
+      <c r="D4">
+        <v>6.6689999999999999E-2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
+        <v>11</v>
+      </c>
+      <c r="D5">
+        <v>0.17510999999999999</v>
+      </c>
+    </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" t="s">
+        <v>13</v>
+      </c>
+      <c r="D6">
+        <v>4.1880000000000001E-2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>14</v>
+      </c>
+      <c r="B7" t="s">
+        <v>15</v>
+      </c>
+      <c r="D7">
+        <v>2.1112899999999999</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A8" t="s">
+        <v>17</v>
+      </c>
+      <c r="B8" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A9" t="s">
+        <v>16</v>
+      </c>
+      <c r="B9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A10" t="s">
+        <v>20</v>
+      </c>
+      <c r="B10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A11" t="s">
+        <v>21</v>
+      </c>
+      <c r="B11" t="s">
+        <v>23</v>
       </c>
     </row>
   </sheetData>

--- a/data/loads.xlsx
+++ b/data/loads.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20417"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Keks-repo\KEKS\data\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Keks-repo\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{56D3FF1F-8156-4B54-8110-95957B8D63D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E47209F-4D8E-4493-AE20-A5E10C7CE055}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3015" yWindow="1590" windowWidth="21600" windowHeight="13185" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="9180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="24" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="30">
   <si>
     <t>name</t>
   </si>
@@ -40,6 +40,9 @@
     <t>Industry_1</t>
   </si>
   <si>
+    <t>AC</t>
+  </si>
+  <si>
     <t>kritis</t>
   </si>
   <si>
@@ -55,22 +58,22 @@
     <t>industry_thermal</t>
   </si>
   <si>
-    <t>Industry_1_thermal</t>
+    <t>Industry_1_HT</t>
+  </si>
+  <si>
+    <t>thermal</t>
   </si>
   <si>
     <t>kritis_thermal</t>
   </si>
   <si>
-    <t>Kritis_1_thermal</t>
-  </si>
-  <si>
-    <t>residential_thermal</t>
-  </si>
-  <si>
-    <t>Residential_1_thermal</t>
-  </si>
-  <si>
-    <t>residential2_thermal</t>
+    <t>Kritis_1_HT</t>
+  </si>
+  <si>
+    <t>residential_HT</t>
+  </si>
+  <si>
+    <t>Residential_1_HT</t>
   </si>
   <si>
     <t>residential2</t>
@@ -79,19 +82,34 @@
     <t>Residential_2</t>
   </si>
   <si>
-    <t>Residential_2_thermal</t>
-  </si>
-  <si>
-    <t>residential_3</t>
-  </si>
-  <si>
-    <t>residential3_thermal</t>
+    <t>residential2_HT</t>
+  </si>
+  <si>
+    <t>Residential_2_HT</t>
+  </si>
+  <si>
+    <t>residential2_LT</t>
+  </si>
+  <si>
+    <t>Residential_2_LT</t>
+  </si>
+  <si>
+    <t>residential3</t>
   </si>
   <si>
     <t>Residential_3</t>
   </si>
   <si>
-    <t>Residential_3_thermal</t>
+    <t>residential3_HT</t>
+  </si>
+  <si>
+    <t>Residential_3_HT</t>
+  </si>
+  <si>
+    <t>residential3_LT</t>
+  </si>
+  <si>
+    <t>Residential_3_LT</t>
   </si>
 </sst>
 </file>
@@ -431,8 +449,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:D11"/>
+  <dimension ref="A1:D13"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <cols>
+    <col min="1" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
@@ -455,27 +476,36 @@
       <c r="B2" t="s">
         <v>5</v>
       </c>
+      <c r="C2" t="s">
+        <v>6</v>
+      </c>
       <c r="D2">
         <v>5.6959999999999997E-2</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>7</v>
+      </c>
+      <c r="B3" t="s">
+        <v>8</v>
+      </c>
+      <c r="C3" t="s">
         <v>6</v>
       </c>
-      <c r="B3" t="s">
-        <v>7</v>
-      </c>
       <c r="D3">
-        <v>6.0599999999999994E-3</v>
+        <v>6.0600000000000003E-3</v>
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="B4" t="s">
-        <v>9</v>
+        <v>10</v>
+      </c>
+      <c r="C4" t="s">
+        <v>6</v>
       </c>
       <c r="D4">
         <v>6.6689999999999999E-2</v>
@@ -483,10 +513,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>12</v>
+      </c>
+      <c r="C5" t="s">
+        <v>13</v>
       </c>
       <c r="D5">
         <v>0.17510999999999999</v>
@@ -494,9 +527,12 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="B6" t="s">
+        <v>15</v>
+      </c>
+      <c r="C6" t="s">
         <v>13</v>
       </c>
       <c r="D6">
@@ -505,10 +541,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="B7" t="s">
-        <v>15</v>
+        <v>17</v>
+      </c>
+      <c r="C7" t="s">
+        <v>13</v>
       </c>
       <c r="D7">
         <v>2.1112899999999999</v>
@@ -516,34 +555,86 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B8" t="s">
-        <v>18</v>
+        <v>19</v>
+      </c>
+      <c r="C8" t="s">
+        <v>6</v>
+      </c>
+      <c r="D8">
+        <v>2.001E-2</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="B9" t="s">
-        <v>19</v>
+        <v>21</v>
+      </c>
+      <c r="C9" t="s">
+        <v>13</v>
+      </c>
+      <c r="D9">
+        <v>2.111E-2</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="B10" t="s">
-        <v>22</v>
+        <v>23</v>
+      </c>
+      <c r="C10" t="s">
+        <v>13</v>
+      </c>
+      <c r="D10">
+        <v>0.63175000000000003</v>
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="B11" t="s">
-        <v>23</v>
+        <v>25</v>
+      </c>
+      <c r="C11" t="s">
+        <v>6</v>
+      </c>
+      <c r="D11">
+        <v>3.3340000000000002E-2</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A12" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" t="s">
+        <v>13</v>
+      </c>
+      <c r="D12">
+        <v>3.5180000000000003E-2</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+      <c r="A13" t="s">
+        <v>28</v>
+      </c>
+      <c r="B13" t="s">
+        <v>29</v>
+      </c>
+      <c r="C13" t="s">
+        <v>13</v>
+      </c>
+      <c r="D13">
+        <v>1.05291</v>
       </c>
     </row>
   </sheetData>

--- a/data/loads.xlsx
+++ b/data/loads.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Keks-repo\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8E47209F-4D8E-4493-AE20-A5E10C7CE055}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{21F58A21-E846-4CE5-8FA0-6B52D3C34797}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="36" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="0" yWindow="0" windowWidth="21570" windowHeight="9180" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="40" uniqueCount="32">
   <si>
     <t>name</t>
   </si>
@@ -40,9 +40,6 @@
     <t>Industry_1</t>
   </si>
   <si>
-    <t>AC</t>
-  </si>
-  <si>
     <t>kritis</t>
   </si>
   <si>
@@ -61,9 +58,6 @@
     <t>Industry_1_HT</t>
   </si>
   <si>
-    <t>thermal</t>
-  </si>
-  <si>
     <t>kritis_thermal</t>
   </si>
   <si>
@@ -110,6 +104,18 @@
   </si>
   <si>
     <t>Residential_3_LT</t>
+  </si>
+  <si>
+    <t>industry_AC</t>
+  </si>
+  <si>
+    <t>kritis_AC</t>
+  </si>
+  <si>
+    <t>residential_AC</t>
+  </si>
+  <si>
+    <t>residential_thermal</t>
   </si>
 </sst>
 </file>
@@ -453,6 +459,7 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="14.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" x14ac:dyDescent="0.25">
@@ -477,7 +484,7 @@
         <v>5</v>
       </c>
       <c r="C2" t="s">
-        <v>6</v>
+        <v>28</v>
       </c>
       <c r="D2">
         <v>5.6959999999999997E-2</v>
@@ -485,13 +492,13 @@
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
+        <v>6</v>
+      </c>
+      <c r="B3" t="s">
         <v>7</v>
       </c>
-      <c r="B3" t="s">
-        <v>8</v>
-      </c>
       <c r="C3" t="s">
-        <v>6</v>
+        <v>29</v>
       </c>
       <c r="D3">
         <v>6.0600000000000003E-3</v>
@@ -499,13 +506,13 @@
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
+        <v>8</v>
+      </c>
+      <c r="B4" t="s">
         <v>9</v>
       </c>
-      <c r="B4" t="s">
-        <v>10</v>
-      </c>
       <c r="C4" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D4">
         <v>6.6689999999999999E-2</v>
@@ -513,13 +520,13 @@
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
+        <v>10</v>
+      </c>
+      <c r="B5" t="s">
         <v>11</v>
       </c>
-      <c r="B5" t="s">
-        <v>12</v>
-      </c>
       <c r="C5" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="D5">
         <v>0.17510999999999999</v>
@@ -527,13 +534,13 @@
     </row>
     <row r="6" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="B6" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="C6" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="D6">
         <v>4.1880000000000001E-2</v>
@@ -541,13 +548,13 @@
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="B7" t="s">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="C7" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="D7">
         <v>2.1112899999999999</v>
@@ -555,13 +562,13 @@
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>18</v>
+        <v>16</v>
       </c>
       <c r="B8" t="s">
-        <v>19</v>
+        <v>17</v>
       </c>
       <c r="C8" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D8">
         <v>2.001E-2</v>
@@ -569,13 +576,13 @@
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="B9" t="s">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="C9" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="D9">
         <v>2.111E-2</v>
@@ -583,13 +590,13 @@
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="B10" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="C10" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="D10">
         <v>0.63175000000000003</v>
@@ -597,13 +604,13 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="B11" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="C11" t="s">
-        <v>6</v>
+        <v>30</v>
       </c>
       <c r="D11">
         <v>3.3340000000000002E-2</v>
@@ -611,13 +618,13 @@
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="B12" t="s">
-        <v>27</v>
+        <v>25</v>
       </c>
       <c r="C12" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="D12">
         <v>3.5180000000000003E-2</v>
@@ -625,13 +632,13 @@
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
       <c r="B13" t="s">
-        <v>29</v>
+        <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>13</v>
+        <v>31</v>
       </c>
       <c r="D13">
         <v>1.05291</v>
